--- a/实体 entity/生物生成/群系与结构的可生成生物/structure.xlsx
+++ b/实体 entity/生物生成/群系与结构的可生成生物/structure.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\游戏机制\生物生成\群系与结构的可生成生物\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993883B3-F46B-45EC-8092-5A42D0347C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="monster" sheetId="1" r:id="rId1"/>
     <sheet name="creature" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -92,12 +86,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -105,15 +99,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -152,35 +139,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -218,7 +194,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -252,7 +228,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -287,10 +262,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -463,16 +437,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.7265625" style="2" customWidth="1"/>
-    <col min="3" max="10" width="10.7265625" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,79 +477,77 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,19 +558,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>